--- a/artfynd/A 22007-2023 artfynd.xlsx
+++ b/artfynd/A 22007-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126903079</v>
       </c>
       <c r="B2" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>126903031</v>
       </c>
       <c r="B3" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
